--- a/stories/arbres/TREE-SAN-012.xlsx
+++ b/stories/arbres/TREE-SAN-012.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rentre au jardin. Papa ouvre le portail. Maman porte le sac. Les mains ont voyagé. Bientôt on mange. Avant de manger, savon. Après les toilettes, savon aussi. Eau, savon, rincer, essuyer.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ils ont pris le train. Lila a touché la barre. Au jardin, papa dit : avant de manger, on lave. Lila ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Après les toilettes du quai, elle avait déjà pris le savon.</t>
+          <t>Ils ont pris le train. Lila a touché la barre. Au jardin, Avant de manger, on lave. Lila ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Après les toilettes du quai, elle avait déjà pris le savon.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Ils ont pris le train. Lila a touché la barre. Au jardin,
+papa|Avant de manger, on lave.
+narrateur|Lila ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Après les toilettes du quai, elle avait déjà pris le savon.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1863,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Lila se lave. Avec quoi ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2036,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Les mains de Lila sentent le savon. Avant de manger, c'est fait. Après les toilettes, c'était fait.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2231,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2211,7 +2260,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Tom frotte aussi. Savon. Lila dit : avant de manger. Après les toilettes, pareil. Ils essuient. Maman pose le goûter.</t>
+          <t>Tom frotte aussi. Savon. Avant de manger. Après les toilettes, pareil. Ils essuient. Maman pose le goûter.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2349,6 +2398,12 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Tom frotte aussi. Savon.
+enfant-f|Avant de manger. Après les toilettes, pareil. Ils essuient. Maman pose le goûter.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2539,6 +2594,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2701,6 +2761,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Tom et Lila ont le savon. Avant de manger. Après les toilettes. Ils essuient près du robinet.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2863,6 +2928,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3025,6 +3095,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Lila lave au savon. Avant de manger. Après les toilettes. Tom tend la serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3187,6 +3262,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3349,6 +3429,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Lila a le savon. Avant de manger. Après les toilettes. Tom dit merci. Ils rentrent.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3511,6 +3596,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3673,6 +3763,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Léa chante : savon, savon. Lila lave avant de manger. Après les toilettes, elle savait déjà. Elles rincent.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3863,6 +3958,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4025,6 +4125,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Léa chante savon. Avant de manger. Après les toilettes. Lila rince. Une goutte tombe.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4187,6 +4292,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4349,6 +4459,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Lila prend le savon. Avant de manger. Après les toilettes. Léa essuie.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4511,6 +4626,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4673,6 +4793,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Lila a lavé au savon. Avant de manger. Après les toilettes. Léa ferme le robinet.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4835,6 +4960,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4859,7 +4989,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Sami ouvre le robinet. Lila prend le savon. Avant de manger. Après les toilettes, déjà fait. Papa dit : bien.</t>
+          <t>Sami ouvre le robinet. Lila prend le savon. Avant de manger. Après les toilettes, déjà fait. Bien.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -4997,6 +5127,12 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sami ouvre le robinet. Lila prend le savon. Avant de manger. Après les toilettes, déjà fait.
+papa|Bien.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5187,6 +5323,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5349,6 +5490,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Sami compte. Lila a le savon. Avant de manger. Après les toilettes. Ils tapent dans les mains.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5511,6 +5657,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5673,6 +5824,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Lila lave au savon. Avant de manger. Après les toilettes. Sami pose le savon.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5835,6 +5991,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5997,6 +6158,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Lila a pris le savon. Avant de manger. Après les toilettes. Sami range la serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6159,6 +6325,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6183,7 +6354,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Ils ont pris le bus. Lila a tenu le ticket. Au jardin, maman dit : avant de manger, savon. Lila lave. Après les toilettes de la gare, savon aussi. Elle rince. Elle essuie. Les mains sont propres.</t>
+          <t>Ils ont pris le bus. Lila a tenu le ticket. Au jardin, Avant de manger, savon. Lila lave. Après les toilettes de la gare, savon aussi. Elle rince. Elle essuie. Les mains sont propres.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6321,6 +6492,13 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Ils ont pris le bus. Lila a tenu le ticket. Au jardin,
+maman|Avant de manger, savon.
+narrateur|Lila lave. Après les toilettes de la gare, savon aussi. Elle rince. Elle essuie. Les mains sont propres.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6501,6 +6679,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Après le bus, Lila prend quoi ?</t>
         </is>
       </c>
     </row>
@@ -6669,6 +6852,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Le bus est loin. Les mains sentent le savon. Avant de manger. Après les toilettes.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6857,6 +7045,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7021,6 +7214,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Tom attend son tour. Lila a le savon. Avant de manger. Après les toilettes. Tom frotte ensuite.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7211,6 +7409,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7373,6 +7576,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Lila a le savon. Avant de manger. Après les toilettes. Tom attend son tour, puis frotte.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7535,6 +7743,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7697,6 +7910,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Lila lave au savon. Avant de manger. Après les toilettes. Le bus est loin.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7859,6 +8077,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8021,6 +8244,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Lila a pris le savon. Avant de manger. Après les toilettes. Tom s'assoit au jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8183,6 +8411,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8345,6 +8578,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Léa tend la serviette. Lila a frotté au savon. Avant de manger. Après les toilettes, pareil.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8535,6 +8773,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8697,6 +8940,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Léa tend la serviette. Lila a le savon. Avant de manger. Après les toilettes.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8859,6 +9107,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9021,6 +9274,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Lila prend le savon. Avant de manger. Après les toilettes. Léa sent ses mains propres.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9183,6 +9441,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9207,7 +9470,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Lila a lavé au savon. Avant de manger. Après les toilettes. Léa dit : on peut manger.</t>
+          <t>Le soir, Lila a lavé au savon. Avant de manger. Après les toilettes. On peut manger.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9345,6 +9608,12 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Lila a lavé au savon. Avant de manger. Après les toilettes.
+enfant-f|On peut manger.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9507,6 +9776,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9669,6 +9943,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sami compte jusqu'à cinq. Lila frotte au savon. Avant de manger. Après les toilettes. Ils essuient ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9859,6 +10138,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10021,6 +10305,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Sami compte jusqu'à cinq. Lila a le savon. Avant de manger. Après les toilettes.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10183,6 +10472,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10345,6 +10639,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Lila lave au savon. Avant de manger. Après les toilettes. Sami essuie trop vite, puis recommence doux.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10507,6 +10806,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10669,6 +10973,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Lila a pris le savon. Avant de manger. Après les toilettes. Sami ferme l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10831,6 +11140,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10993,6 +11307,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Ils ont pris la voiture. Lila a touché la ceinture. Au jardin, papa ouvre le robinet. Avant de manger, Lila prend le savon. Après les toilettes de l'aire, elle avait déjà lavé. Elle rince.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11173,6 +11492,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Après la voiture, Lila prend quoi ?</t>
         </is>
       </c>
     </row>
@@ -11341,6 +11665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|La voiture est au garage. Les mains sont propres. Savon avant de manger. Savon après les toilettes.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11531,6 +11860,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11555,7 +11889,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Tom tient le savon. Lila frotte. Avant de manger. Après les toilettes. Maman dit : on peut s'asseoir.</t>
+          <t>Tom tient le savon. Lila frotte. Avant de manger. Après les toilettes. On peut s'asseoir.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11693,6 +12027,12 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Tom tient le savon. Lila frotte. Avant de manger. Après les toilettes.
+maman|On peut s'asseoir.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11883,6 +12223,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11907,7 +12252,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Le matin, Tom tient le savon. Lila frotte. Avant de manger. Après les toilettes. Maman dit : on s'assoit.</t>
+          <t>Le matin, Tom tient le savon. Lila frotte. Avant de manger. Après les toilettes. On s'assoit.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12045,6 +12390,12 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Tom tient le savon. Lila frotte. Avant de manger. Après les toilettes.
+maman|On s'assoit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12207,6 +12558,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12369,6 +12725,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Lila lave au savon. Avant de manger. Après les toilettes. La voiture dort au garage.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12531,6 +12892,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12693,6 +13059,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Lila a pris le savon. Avant de manger. Après les toilettes. Tom pose le panier.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12855,6 +13226,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13017,6 +13393,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Léa ouvre l'eau. Lila prend le savon. Avant de manger. Après les toilettes. Elles essuient sur la même serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13207,6 +13588,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13369,6 +13755,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Léa ouvre l'eau. Lila a le savon. Avant de manger. Après les toilettes. Elles essuient ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13531,6 +13922,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13693,6 +14089,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Lila prend le savon. Avant de manger. Après les toilettes. Léa plie la serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13855,6 +14256,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13879,7 +14285,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Lila a lavé au savon. Avant de manger. Après les toilettes. Léa dit : les mains sentent bon.</t>
+          <t>Le soir, Lila a lavé au savon. Avant de manger. Après les toilettes. Les mains sentent bon.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14017,6 +14423,12 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Lila a lavé au savon. Avant de manger. Après les toilettes.
+enfant-f|Les mains sentent bon.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14179,6 +14591,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14341,6 +14758,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sami ferme le robinet. Lila a frotté au savon. Avant de manger. Après les toilettes. Papa pose le panier.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14531,6 +14953,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14693,6 +15120,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, Sami ferme le robinet. Lila a le savon. Avant de manger. Après les toilettes. Papa pose le panier.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14855,6 +15287,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15017,6 +15454,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Lila lave au savon. Avant de manger. Après les toilettes. Sami bâille, mains propres.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15179,6 +15621,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15203,7 +15650,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Lila a pris le savon. Avant de manger. Après les toilettes. Sami dit : on mange.</t>
+          <t>Le soir, Lila a pris le savon. Avant de manger. Après les toilettes. On mange.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15341,6 +15788,12 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Lila a pris le savon. Avant de manger. Après les toilettes.
+enfant-m|On mange.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15503,6 +15956,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15521,7 +15979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15559,6 +16017,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-012.xlsx
+++ b/stories/arbres/TREE-SAN-012.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Lila rentre au jardin. Papa ouvre le portail. Maman porte le sac. Les mains ont voyagé. Bientôt on mange. Avant de manger, savon. Après les toilettes, savon aussi. Eau, savon, rincer, essuyer.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1687,6 +1694,7 @@
 narrateur|Lila ouvre l'eau. Elle prend le savon. Elle frotte. Elle rince. Après les toilettes du quai, elle avait déjà pris le savon.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1870,6 +1878,7 @@
           <t>narrateur|Lila se lave. Avec quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2041,6 +2050,7 @@
           <t>narrateur|Les mains de Lila sentent le savon. Avant de manger, c'est fait. Après les toilettes, c'était fait.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2236,6 +2246,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2404,6 +2415,7 @@
 enfant-f|Avant de manger. Après les toilettes, pareil. Ils essuient. Maman pose le goûter.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2599,6 +2611,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2766,6 +2779,7 @@
           <t>narrateur|Le matin, Tom et Lila ont le savon. Avant de manger. Après les toilettes. Ils essuient près du robinet.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2933,6 +2947,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3100,6 +3115,7 @@
           <t>narrateur|Après la sieste, Lila lave au savon. Avant de manger. Après les toilettes. Tom tend la serviette.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3267,6 +3283,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3434,6 +3451,7 @@
           <t>narrateur|Le soir, Lila a le savon. Avant de manger. Après les toilettes. Tom dit merci. Ils rentrent.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3601,6 +3619,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3768,6 +3787,7 @@
           <t>narrateur|Léa chante : savon, savon. Lila lave avant de manger. Après les toilettes, elle savait déjà. Elles rincent.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3963,6 +3983,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4130,6 +4151,7 @@
           <t>narrateur|Le matin, Léa chante savon. Avant de manger. Après les toilettes. Lila rince. Une goutte tombe.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4297,6 +4319,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4464,6 +4487,7 @@
           <t>narrateur|Après la sieste, Lila prend le savon. Avant de manger. Après les toilettes. Léa essuie.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4631,6 +4655,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4798,6 +4823,7 @@
           <t>narrateur|Le soir, Lila a lavé au savon. Avant de manger. Après les toilettes. Léa ferme le robinet.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4965,6 +4991,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5133,6 +5160,7 @@
 papa|Bien.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5328,6 +5356,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5495,6 +5524,7 @@
           <t>narrateur|Le matin, Sami compte. Lila a le savon. Avant de manger. Après les toilettes. Ils tapent dans les mains.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5662,6 +5692,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5829,6 +5860,7 @@
           <t>narrateur|Après la sieste, Lila lave au savon. Avant de manger. Après les toilettes. Sami pose le savon.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5996,6 +6028,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6163,6 +6196,7 @@
           <t>narrateur|Le soir, Lila a pris le savon. Avant de manger. Après les toilettes. Sami range la serviette.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6330,6 +6364,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6499,6 +6534,7 @@
 narrateur|Lila lave. Après les toilettes de la gare, savon aussi. Elle rince. Elle essuie. Les mains sont propres.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6686,6 +6722,7 @@
           <t>narrateur|Après le bus, Lila prend quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6857,6 +6894,7 @@
           <t>narrateur|Le bus est loin. Les mains sentent le savon. Avant de manger. Après les toilettes.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7052,6 +7090,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7219,6 +7258,7 @@
           <t>narrateur|Tom attend son tour. Lila a le savon. Avant de manger. Après les toilettes. Tom frotte ensuite.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7414,6 +7454,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7581,6 +7622,7 @@
           <t>narrateur|Le matin, Lila a le savon. Avant de manger. Après les toilettes. Tom attend son tour, puis frotte.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7748,6 +7790,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7915,6 +7958,7 @@
           <t>narrateur|Après la sieste, Lila lave au savon. Avant de manger. Après les toilettes. Le bus est loin.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8082,6 +8126,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8249,6 +8294,7 @@
           <t>narrateur|Le soir, Lila a pris le savon. Avant de manger. Après les toilettes. Tom s'assoit au jardin.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8416,6 +8462,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8583,6 +8630,7 @@
           <t>narrateur|Léa tend la serviette. Lila a frotté au savon. Avant de manger. Après les toilettes, pareil.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8778,6 +8826,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8945,6 +8994,7 @@
           <t>narrateur|Le matin, Léa tend la serviette. Lila a le savon. Avant de manger. Après les toilettes.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9112,6 +9162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9279,6 +9330,7 @@
           <t>narrateur|Après la sieste, Lila prend le savon. Avant de manger. Après les toilettes. Léa sent ses mains propres.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9446,6 +9498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9614,6 +9667,7 @@
 enfant-f|On peut manger.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9781,6 +9835,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9948,6 +10003,7 @@
           <t>narrateur|Sami compte jusqu'à cinq. Lila frotte au savon. Avant de manger. Après les toilettes. Ils essuient ensemble.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10143,6 +10199,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10310,6 +10367,7 @@
           <t>narrateur|Le matin, Sami compte jusqu'à cinq. Lila a le savon. Avant de manger. Après les toilettes.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10477,6 +10535,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10644,6 +10703,7 @@
           <t>narrateur|Après la sieste, Lila lave au savon. Avant de manger. Après les toilettes. Sami essuie trop vite, puis recommence doux.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10811,6 +10871,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10978,6 +11039,7 @@
           <t>narrateur|Le soir, Lila a pris le savon. Avant de manger. Après les toilettes. Sami ferme l'eau.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11145,6 +11207,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11312,6 +11375,7 @@
           <t>narrateur|Ils ont pris la voiture. Lila a touché la ceinture. Au jardin, papa ouvre le robinet. Avant de manger, Lila prend le savon. Après les toilettes de l'aire, elle avait déjà lavé. Elle rince.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11499,6 +11563,7 @@
           <t>narrateur|Après la voiture, Lila prend quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11670,6 +11735,7 @@
           <t>narrateur|La voiture est au garage. Les mains sont propres. Savon avant de manger. Savon après les toilettes.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11865,6 +11931,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12033,6 +12100,7 @@
 maman|On peut s'asseoir.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12228,6 +12296,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12396,6 +12465,7 @@
 maman|On s'assoit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12563,6 +12633,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12730,6 +12801,7 @@
           <t>narrateur|Après la sieste, Lila lave au savon. Avant de manger. Après les toilettes. La voiture dort au garage.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12897,6 +12969,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13064,6 +13137,7 @@
           <t>narrateur|Le soir, Lila a pris le savon. Avant de manger. Après les toilettes. Tom pose le panier.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13231,6 +13305,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13398,6 +13473,7 @@
           <t>narrateur|Léa ouvre l'eau. Lila prend le savon. Avant de manger. Après les toilettes. Elles essuient sur la même serviette.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13593,6 +13669,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13760,6 +13837,7 @@
           <t>narrateur|Le matin, Léa ouvre l'eau. Lila a le savon. Avant de manger. Après les toilettes. Elles essuient ensemble.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13927,6 +14005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14094,6 +14173,7 @@
           <t>narrateur|Après la sieste, Lila prend le savon. Avant de manger. Après les toilettes. Léa plie la serviette.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14261,6 +14341,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14429,6 +14510,7 @@
 enfant-f|Les mains sentent bon.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14596,6 +14678,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14763,6 +14846,7 @@
           <t>narrateur|Sami ferme le robinet. Lila a frotté au savon. Avant de manger. Après les toilettes. Papa pose le panier.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14958,6 +15042,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15125,6 +15210,7 @@
           <t>narrateur|Le matin, Sami ferme le robinet. Lila a le savon. Avant de manger. Après les toilettes. Papa pose le panier.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15292,6 +15378,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15459,6 +15546,7 @@
           <t>narrateur|Après la sieste, Lila lave au savon. Avant de manger. Après les toilettes. Sami bâille, mains propres.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15626,6 +15714,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15794,6 +15883,7 @@
 enfant-m|On mange.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15961,6 +16051,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15979,7 +16070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16024,6 +16115,20 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16038,7 +16143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16225,6 +16330,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
